--- a/branches/migration/2026.0.0-template-v0.13.2/CodeSystem-mii-cs-consent-version-modules.xlsx
+++ b/branches/migration/2026.0.0-template-v0.13.2/CodeSystem-mii-cs-consent-version-modules.xlsx
@@ -67,7 +67,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-31T20:16:52+00:00</t>
+    <t>2026-08-31T20:36:21+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/migration/2026.0.0-template-v0.13.2/CodeSystem-mii-cs-consent-version-modules.xlsx
+++ b/branches/migration/2026.0.0-template-v0.13.2/CodeSystem-mii-cs-consent-version-modules.xlsx
@@ -37,7 +37,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>2026.0.0</t>
+    <t>2027.0.0-ballot.rc1</t>
   </si>
   <si>
     <t>Name</t>
@@ -67,7 +67,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-31T20:36:21+00:00</t>
+    <t>2026-08-31T20:57:36+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/migration/2026.0.0-template-v0.13.2/CodeSystem-mii-cs-consent-version-modules.xlsx
+++ b/branches/migration/2026.0.0-template-v0.13.2/CodeSystem-mii-cs-consent-version-modules.xlsx
@@ -67,7 +67,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-31T20:57:36+00:00</t>
+    <t>2026-08-31T21:05:22+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
